--- a/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
+++ b/files/港岛-香港仔及鸭脷洲-Blue Coast II.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,14 +45,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -64,7 +69,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -75,7 +80,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -86,7 +91,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -96,9 +101,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -171,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -188,19 +214,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,10 +232,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -599,7 +637,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -26378,1510 +26416,1510 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Blue Coast II - 3座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>279 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>271 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$4,409万
+$4409万
 $34,800/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$4,198万
+$4198万
 $34,300/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,105万
+$1105万
 $23,812/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,094万
+$1094万
 $24,527/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,133万
+$1133万
 $23,895/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,107万
+$1107万
 $24,980/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,990万
+$1990万
 $26,217/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,848万
+$1848万
 $25,740/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,894万
+$1894万
 $25,988/呎
 (25年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$4,308万
+$4308万
 $34,000/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,966万
+$3966万
 $32,400/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,069万
+$1069万
 $23,047/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,090万
+$1090万
 $24,430/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,096万
+$1096万
 $23,129/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,099万
+$1099万
 $24,817/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,941万
+$1941万
 $25,569/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,834万
+$1834万
 $25,536/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,848万
+$1848万
 $25,344/呎
 (25年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$4,080万
+$4080万
 $32,200/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$4,039万
+$4039万
 $33,000/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,066万
+$1066万
 $22,963/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,085万
+$1085万
 $24,336/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,092万
+$1092万
 $23,042/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,095万
+$1095万
 $24,722/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,932万
+$1932万
 $25,455/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,825万
+$1825万
 $25,421/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,871万
+$1871万
 $25,668/呎
 (25年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$4,004万
+$4004万
 $31,600/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,819万
+$3819万
 $31,200/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,061万
+$1061万
 $22,873/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,081万
+$1081万
 $24,242/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,088万
+$1088万
 $22,956/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,088万
+$1088万
 $24,571/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,923万
+$1923万
 $25,341/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,817万
+$1817万
 $25,308/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,863万
+$1863万
 $25,551/呎
 (25年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,915万
+$3915万
 $30,900/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,623万
+$3623万
 $29,600/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,057万
+$1057万
 $22,787/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,077万
+$1077万
 $24,150/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,084万
+$1084万
 $22,867/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,084万
+$1084万
 $24,476/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,973万
+$1973万
 $26,000/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,809万
+$1809万
 $25,194/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,854万
+$1854万
 $25,438/呎
 (25年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,877万
+$3877万
 $30,600/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,586万
+$3586万
 $29,300/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,053万
+$1053万
 $22,700/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,073万
+$1073万
 $24,061/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,080万
+$1080万
 $22,783/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,080万
+$1080万
 $24,386/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,906万
+$1906万
 $25,115/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,801万
+$1801万
 $25,081/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,846万
+$1846万
 $25,324/呎
 (25年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,801万
+$3801万
 $30,000/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,623万
+$3623万
 $29,600/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,049万
+$1049万
 $22,614/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,069万
+$1069万
 $23,971/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,076万
+$1076万
 $22,696/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,075万
+$1075万
 $24,269/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,887万
+$1887万
 $24,864/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,783万
+$1783万
 $24,833/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,797万
+$1797万
 $24,649/呎
 (25年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,788万
+$3788万
 $29,900/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,586万
+$3586万
 $29,300/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,076万
+$1076万
 $23,185/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,065万
+$1065万
 $23,879/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,072万
+$1072万
 $22,610/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,071万
+$1071万
 $24,176/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,869万
+$1869万
 $24,621/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,765万
+$1765万
 $24,586/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,779万
+$1779万
 $24,405/呎
 (25年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,776万
+$3776万
 $29,803/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,537万
+$3537万
 $28,900/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,033万
+$1033万
 $22,254/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,071万
+$1071万
 $24,018/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,089万
+$1089万
 $22,981/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,059万
+$1059万
 $23,905/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,891万
+$1891万
 $24,920/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,756万
+$1756万
 $24,464/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,770万
+$1770万
 $24,284/呎
 (25年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,738万
+$3738万
 $29,500/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,476万
+$3476万
 $28,400/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,020万
+$1020万
 $21,978/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,042万
+$1042万
 $23,374/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,046万
+$1046万
 $22,059/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,048万
+$1048万
 $23,666/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,850万
+$1850万
 $24,375/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,748万
+$1748万
 $24,343/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,761万
+$1761万
 $24,162/呎
 (25年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,712万
+$3712万
 $29,300/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,476万
+$3476万
 $28,400/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,044万
+$1044万
 $22,498/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,037万
+$1037万
 $23,247/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,040万
+$1040万
 $21,935/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,042万
+$1042万
 $23,533/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,872万
+$1872万
 $24,661/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,738万
+$1738万
 $24,209/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,752万
+$1752万
 $24,029/呎
 (25年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,687万
+$3687万
 $29,100/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,488万
+$3488万
 $28,500/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,009万
+$1009万
 $21,739/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,019万
+$1019万
 $22,854/呎
 (25年-05月)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,034万
+$1034万
 $21,819/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,037万
+$1037万
 $23,409/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,830万
+$1830万
 $24,111/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,700万
+$1700万
 $23,670/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,749万
+$1749万
 $23,995/呎
 (24年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,662万
+$3662万
 $28,900/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,403万
+$3403万
 $27,800/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,032万
+$1032万
 $22,250/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,026万
+$1026万
 $22,996/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,028万
+$1028万
 $21,698/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,031万
+$1031万
 $23,278/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,851万
+$1851万
 $24,390/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,719万
+$1719万
 $23,946/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,740万
+$1740万
 $23,863/呎
 (25年-02月)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,624万
+$3624万
 $28,600/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,403万
+$3403万
 $27,800/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,026万
+$1026万
 $22,108/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,020万
+$1020万
 $22,868/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,022万
+$1022万
 $21,559/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,026万
+$1026万
 $23,151/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,810万
+$1810万
 $23,846/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,710万
+$1710万
 $23,813/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,730万
+$1730万
 $23,731/呎
 (24年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,598万
+$3598万
 $28,400/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,342万
+$3342万
 $27,304/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,020万
+$1020万
 $21,985/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,014万
+$1014万
 $22,742/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,016万
+$1016万
 $21,441/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,020万
+$1020万
 $23,025/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,800万
+$1800万
 $23,715/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,672万
+$1672万
 $23,283/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,720万
+$1720万
 $23,601/呎
 (25年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,573万
+$3573万
 $28,200/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,366万
+$3366万
 $27,500/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,015万
+$1015万
 $21,866/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,009万
+$1009万
 $22,621/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,011万
+$1011万
 $21,325/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,014万
+$1014万
 $22,898/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,790万
+$1790万
 $23,586/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,663万
+$1663万
 $23,156/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,663万
+$1663万
 $22,809/呎
 (25年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,573万
+$3573万
 $28,200/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,360万
+$3360万
 $27,450/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
-$1,009万
+$1009万
 $21,746/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
-$1,003万
+$1003万
 $22,496/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,005万
+$1005万
 $21,207/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,009万
+$1009万
 $22,774/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,780万
+$1780万
 $23,457/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,653万
+$1653万
 $23,028/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,654万
+$1654万
 $22,684/呎
 (25年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,560万
+$3560万
 $28,100/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,354万
+$3354万
 $27,400/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $975万
@@ -27889,7 +27927,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $998万
@@ -27897,70 +27935,70 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,000万
+$1000万
 $21,093/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,003万
+$1003万
 $22,650/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,771万
+$1771万
 $23,329/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,673万
+$1673万
 $23,297/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,666万
+$1666万
 $22,857/呎
 (25年-06月)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,548万
+$3548万
 $28,000/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,342万
+$3342万
 $27,300/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $989万
@@ -27968,7 +28006,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $985万
@@ -27976,7 +28014,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $986万
@@ -27984,7 +28022,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $990万
@@ -27992,54 +28030,54 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,761万
+$1761万
 $23,202/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,664万
+$1664万
 $23,170/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,657万
+$1657万
 $22,734/呎
 (25年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,548万
+$3548万
 $28,000/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,525万
+$3525万
 $28,800/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $958万
@@ -28047,7 +28085,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $982万
@@ -28055,15 +28093,15 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,011万
+$1011万
 $21,321/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $987万
@@ -28071,54 +28109,54 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,753万
+$1753万
 $23,097/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,628万
+$1628万
 $22,674/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,669万
+$1669万
 $22,894/呎
 (25年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,636万
+$3636万
 $28,700/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,427万
+$3427万
 $28,000/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $960万
@@ -28126,7 +28164,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $995万
@@ -28134,15 +28172,15 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,007万
+$1007万
 $21,247/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $984万
@@ -28150,54 +28188,54 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,745万
+$1745万
 $22,995/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,621万
+$1621万
 $22,572/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,668万
+$1668万
 $22,882/呎
 (25年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,535万
+$3535万
 $27,900/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,513万
+$3513万
 $28,700/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $979万
@@ -28205,7 +28243,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $975万
@@ -28213,7 +28251,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $988万
@@ -28221,7 +28259,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $980万
@@ -28229,54 +28267,54 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,738万
+$1738万
 $22,892/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,613万
+$1613万
 $22,471/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,614万
+$1614万
 $22,137/呎
 (25年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,535万
+$3535万
 $27,900/呎
 (26年-03月)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,513万
+$3513万
 $28,700/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $947万
@@ -28284,7 +28322,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $971万
@@ -28292,7 +28330,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $996万
@@ -28300,7 +28338,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $976万
@@ -28308,54 +28346,54 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,730万
+$1730万
 $22,789/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,606万
+$1606万
 $22,370/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,628万
+$1628万
 $22,329/呎
 (25年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$4,004万
+$4004万
 $31,600/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,501万
+$3501万
 $28,600/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $944万
@@ -28363,7 +28401,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $968万
@@ -28371,7 +28409,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $992万
@@ -28379,7 +28417,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $973万
@@ -28387,54 +28425,54 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,722万
+$1722万
 $22,688/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,599万
+$1599万
 $22,270/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,668万
+$1668万
 $22,875/呎
 (25年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,674万
+$3674万
 $29,000/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,501万
+$3501万
 $28,600/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $940万
@@ -28442,7 +28480,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $964万
@@ -28450,7 +28488,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $988万
@@ -28458,7 +28496,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $967万
@@ -28466,54 +28504,54 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,714万
+$1714万
 $22,577/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I30" s="16" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,591万
+$1591万
 $22,162/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,660万
+$1660万
 $22,764/呎
 (25年-05月)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
-$3,649万
+$3649万
 $28,800/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
-$3,501万
+$3501万
 $28,600/呎
 (26年-06月)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $964万
@@ -28521,7 +28559,7 @@
 (24年-12月)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $960万
@@ -28529,7 +28567,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $984万
@@ -28537,7 +28575,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $960万
@@ -28545,38 +28583,38 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,705万
+$1705万
 $22,465/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,583万
+$1583万
 $22,053/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,605万
+$1605万
 $22,012/呎
 (25年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
 招标单位
@@ -28584,7 +28622,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
 招标单位
@@ -28592,7 +28630,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $960万
@@ -28600,7 +28638,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $956万
@@ -28608,7 +28646,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $980万
@@ -28616,7 +28654,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $954万
@@ -28624,38 +28662,38 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,696万
+$1696万
 $22,349/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,557万
+$1557万
 $21,687/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="J31" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,621万
+$1621万
 $22,241/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
 招标单位
@@ -28663,7 +28701,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
+      <c r="C32" s="21" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
 招标单位
@@ -28671,7 +28709,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $956万
@@ -28679,7 +28717,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $952万
@@ -28687,7 +28725,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $952万
@@ -28695,7 +28733,7 @@
 (25年-02月)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $948万
@@ -28703,38 +28741,38 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,688万
+$1688万
 $22,233/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,594万
+$1594万
 $22,202/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,613万
+$1613万
 $22,126/呎
 (24年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
 招标单位
@@ -28742,7 +28780,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
 招标单位
@@ -28750,7 +28788,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $925万
@@ -28758,7 +28796,7 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $965万
@@ -28766,7 +28804,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $961万
@@ -28774,7 +28812,7 @@
 (25年-05月)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $940万
@@ -28782,38 +28820,38 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,679万
+$1679万
 $22,119/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,541万
+$1541万
 $21,462/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="J33" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,605万
+$1605万
 $22,012/呎
 (25年-02月)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>A | 1267呎 (4+房)
 招标单位
@@ -28821,7 +28859,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>B | 1224呎 (4+房)
 招标单位
@@ -28829,7 +28867,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $948万
@@ -28837,7 +28875,7 @@
 (25年-03月)</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $944万
@@ -28845,7 +28883,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $968万
@@ -28853,7 +28891,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
 $932万
@@ -28861,54 +28899,54 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,646万
+$1646万
 $21,686/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,511万
+$1511万
 $21,042/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,529万
+$1529万
 $20,970/呎
 (25年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 1218呎 (4+房)
-$3,654万
+$3654万
 $30,000/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 1181呎 (4+房)
-$3,531万
+$3531万
 $29,900/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 464呎 (2房)
 $922万
@@ -28916,7 +28954,7 @@
 (25年-04月)</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 446呎 (2房)
 $933万
@@ -28924,7 +28962,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $957万
@@ -28932,34 +28970,34 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>F | 443呎 (2房)
-$1,108万
+$1108万
 $25,000/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>G | 759呎 (3房)
-$1,614万
+$1614万
 $21,261/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="I36" s="16" t="inlineStr">
+      <c r="I35" s="20" t="inlineStr">
         <is>
           <t>H | 718呎 (3房)
-$1,557万
+$1557万
 $21,681/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="J35" s="20" t="inlineStr">
         <is>
           <t>J | 729呎 (3房)
-$1,640万
+$1640万
 $22,497/呎
 (24年-11月)</t>
         </is>
@@ -28967,7 +29005,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -28980,1226 +29018,1226 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Blue Coast II - 5座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>279 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>279 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J4" s="19" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>40/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,872万
+$1872万
 $23,340/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$2,016万
+$2016万
 $25,818/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,281万
+$1281万
 $25,169/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,871万
+$1871万
 $24,294/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,151万
+$1151万
 $24,281/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,289万
+$1289万
 $24,009/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,098万
+$1098万
 $22,635/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,200万
+$1200万
 $24,540/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J6" s="16" t="inlineStr">
+      <c r="J5" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,917万
+$1917万
 $24,732/呎
 (24年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>39/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,857万
+$1857万
 $23,153/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,944万
+$1944万
 $24,890/呎
 (25年-05月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,271万
+$1271万
 $24,969/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,856万
+$1856万
 $24,101/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,113万
+$1113万
 $23,477/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,316万
+$1316万
 $24,512/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,048万
+$1048万
 $21,612/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,158万
+$1158万
 $23,681/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J7" s="16" t="inlineStr">
+      <c r="J6" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,908万
+$1908万
 $24,622/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>38/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,848万
+$1848万
 $23,044/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,935万
+$1935万
 $24,772/呎
 (25年-04月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,229万
+$1229万
 $24,147/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,847万
+$1847万
 $23,986/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,107万
+$1107万
 $23,361/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,269万
+$1269万
 $23,629/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,043万
+$1043万
 $21,511/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,183万
+$1183万
 $24,196/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J8" s="16" t="inlineStr">
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,846万
+$1846万
 $23,814/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>37/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,839万
+$1839万
 $22,934/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,981万
+$1981万
 $25,369/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,259万
+$1259万
 $24,731/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,838万
+$1838万
 $23,871/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,102万
+$1102万
 $23,245/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,259万
+$1259万
 $23,443/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,068万
+$1068万
 $22,031/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,142万
+$1142万
 $23,350/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J9" s="16" t="inlineStr">
+      <c r="J8" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,890万
+$1890万
 $24,392/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>36/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,884万
+$1884万
 $23,488/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,891万
+$1891万
 $24,215/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,217万
+$1217万
 $23,917/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,829万
+$1829万
 $23,757/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,096万
+$1096万
 $23,129/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,285万
+$1285万
 $23,931/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,064万
+$1064万
 $21,928/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,133万
+$1133万
 $23,176/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J10" s="16" t="inlineStr">
+      <c r="J9" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,882万
+$1882万
 $24,277/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>35/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,822万
+$1822万
 $22,714/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,882万
+$1882万
 $24,099/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,212万
+$1212万
 $23,804/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,820万
+$1820万
 $23,643/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,091万
+$1091万
 $23,015/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,275万
+$1275万
 $23,743/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,029万
+$1029万
 $21,210/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,158万
+$1158万
 $23,675/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J11" s="16" t="inlineStr">
+      <c r="J10" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,820万
+$1820万
 $23,481/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,813万
+$1813万
 $22,606/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,928万
+$1928万
 $24,681/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,206万
+$1206万
 $23,690/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,812万
+$1812万
 $23,530/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,086万
+$1086万
 $22,901/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,265万
+$1265万
 $23,553/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,068万
+$1068万
 $22,010/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,149万
+$1149万
 $23,497/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J12" s="16" t="inlineStr">
+      <c r="J11" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,864万
+$1864万
 $24,050/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,795万
+$1795万
 $22,384/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,855万
+$1855万
 $23,746/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,229万
+$1229万
 $24,138/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,794万
+$1794万
 $23,297/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,078万
+$1078万
 $22,741/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,220万
+$1220万
 $22,728/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,062万
+$1062万
 $21,907/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I12" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,109万
+$1109万
 $22,685/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="J13" s="16" t="inlineStr">
+      <c r="J12" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,803万
+$1803万
 $23,261/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,829万
+$1829万
 $22,805/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,836万
+$1836万
 $23,512/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,216万
+$1216万
 $23,898/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,776万
+$1776万
 $23,066/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,070万
+$1070万
 $22,582/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,212万
+$1212万
 $22,570/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,058万
+$1058万
 $21,806/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,134万
+$1134万
 $23,194/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J14" s="16" t="inlineStr">
+      <c r="J13" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,847万
+$1847万
 $23,827/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,819万
+$1819万
 $22,681/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,826万
+$1826万
 $23,383/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,176万
+$1176万
 $23,094/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,766万
+$1766万
 $22,940/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,064万
+$1064万
 $22,449/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,239万
+$1239万
 $23,065/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,053万
+$1053万
 $21,703/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,127万
+$1127万
 $23,047/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J15" s="16" t="inlineStr">
+      <c r="J14" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,838万
+$1838万
 $23,715/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,758万
+$1758万
 $21,919/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,869万
+$1869万
 $23,931/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,203万
+$1203万
 $23,639/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,757万
+$1757万
 $22,814/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,088万
+$1088万
 $22,949/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,229万
+$1229万
 $22,894/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,005万
+$1005万
 $20,718/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,119万
+$1119万
 $22,875/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J15" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,777万
+$1777万
 $22,930/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,748万
+$1748万
 $21,799/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,806万
+$1806万
 $23,128/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,196万
+$1196万
 $23,507/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,747万
+$1747万
 $22,690/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,081万
+$1081万
 $22,804/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,222万
+$1222万
 $22,747/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,029万
+$1029万
 $21,221/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,111万
+$1111万
 $22,728/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J17" s="16" t="inlineStr">
+      <c r="J16" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,820万
+$1820万
 $23,480/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,789万
+$1789万
 $22,310/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,796万
+$1796万
 $23,000/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,156万
+$1156万
 $22,719/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,738万
+$1738万
 $22,565/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,074万
+$1074万
 $22,656/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,214万
+$1214万
 $22,598/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,038万
+$1038万
 $21,400/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,104万
+$1104万
 $22,579/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J18" s="16" t="inlineStr">
+      <c r="J17" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,811万
+$1811万
 $23,364/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,780万
+$1780万
 $22,190/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,838万
+$1838万
 $23,540/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,150万
+$1150万
 $22,595/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,706万
+$1706万
 $22,149/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,037万
+$1037万
 $21,871/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,206万
+$1206万
 $22,454/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $991万
@@ -30207,315 +30245,315 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,097万
+$1097万
 $22,434/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J19" s="16" t="inlineStr">
+      <c r="J18" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,802万
+$1802万
 $23,246/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,770万
+$1770万
 $22,067/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,828万
+$1828万
 $23,411/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,177万
+$1177万
 $23,126/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,696万
+$1696万
 $22,029/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,060万
+$1060万
 $22,365/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,198万
+$1198万
 $22,307/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,015万
+$1015万
 $20,924/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,059万
+$1059万
 $21,661/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J20" s="16" t="inlineStr">
+      <c r="J19" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,793万
+$1793万
 $23,132/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,760万
+$1760万
 $21,948/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,767万
+$1767万
 $22,626/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,171万
+$1171万
 $22,998/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,709万
+$1709万
 $22,197/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,053万
+$1053万
 $22,217/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,190万
+$1190万
 $22,164/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,023万
+$1023万
 $21,101/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,083万
+$1083万
 $22,145/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J21" s="16" t="inlineStr">
+      <c r="J20" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,784万
+$1784万
 $23,015/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,750万
+$1750万
 $21,827/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,808万
+$1808万
 $23,156/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,164万
+$1164万
 $22,872/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,700万
+$1700万
 $22,075/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,017万
+$1017万
 $21,451/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,184万
+$1184万
 $22,043/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
-$1,005万
+$1005万
 $20,730/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,046万
+$1046万
 $21,401/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J22" s="16" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,775万
+$1775万
 $22,901/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,692万
+$1692万
 $21,094/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,799万
+$1799万
 $23,029/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,125万
+$1125万
 $22,104/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,690万
+$1690万
 $21,955/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,010万
+$1010万
 $21,312/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,144万
+$1144万
 $21,304/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $985万
@@ -30523,62 +30561,62 @@
 (25年-06月)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,071万
+$1071万
 $21,904/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J23" s="16" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,766万
+$1766万
 $22,788/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,731万
+$1731万
 $21,587/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,738万
+$1738万
 $22,256/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,152万
+$1152万
 $22,623/呎
 (24年-10月)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,681万
+$1681万
 $21,834/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $998万
@@ -30586,15 +30624,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,171万
+$1171万
 $21,804/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $968万
@@ -30602,62 +30640,62 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,035万
+$1035万
 $21,170/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J24" s="16" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,708万
+$1708万
 $22,041/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,676万
+$1676万
 $20,899/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,782万
+$1782万
 $22,817/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,147万
+$1147万
 $22,536/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,675万
+$1675万
 $21,753/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $994万
@@ -30665,15 +30703,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,133万
+$1133万
 $21,101/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $992万
@@ -30681,78 +30719,78 @@
 (25年-01月)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,037万
+$1037万
 $21,207/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J25" s="16" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,751万
+$1751万
 $22,591/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,718万
+$1718万
 $21,424/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,725万
+$1725万
 $22,090/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,110万
+$1110万
 $21,817/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,600万
+$1600万
 $20,783/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
-$1,019万
+$1019万
 $21,500/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,162万
+$1162万
 $21,629/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $988万
@@ -30760,62 +30798,62 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,057万
+$1057万
 $21,609/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J26" s="16" t="inlineStr">
+      <c r="J25" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,694万
+$1694万
 $21,865/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,712万
+$1712万
 $21,344/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,769万
+$1769万
 $22,645/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,138万
+$1138万
 $22,365/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,640万
+$1640万
 $21,305/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $986万
@@ -30823,15 +30861,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,124万
+$1124万
 $20,935/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $956万
@@ -30839,62 +30877,62 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,052万
+$1052万
 $21,524/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J27" s="16" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,688万
+$1688万
 $21,778/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,705万
+$1705万
 $21,263/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,712万
+$1712万
 $21,922/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,102万
+$1102万
 $21,652/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,634万
+$1634万
 $21,226/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $982万
@@ -30902,15 +30940,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,120万
+$1120万
 $20,851/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $952万
@@ -30918,62 +30956,62 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,019万
+$1019万
 $20,834/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J28" s="16" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,730万
+$1730万
 $22,321/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,699万
+$1699万
 $21,182/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,755万
+$1755万
 $22,474/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,130万
+$1130万
 $22,196/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,628万
+$1628万
 $21,144/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $978万
@@ -30981,15 +31019,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,148万
+$1148万
 $21,374/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $976万
@@ -30997,62 +31035,62 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,044万
+$1044万
 $21,352/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J29" s="16" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,723万
+$1723万
 $22,232/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,692万
+$1692万
 $21,097/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,699万
+$1699万
 $21,753/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,125万
+$1125万
 $22,108/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,643万
+$1643万
 $21,340/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $980万
@@ -31060,15 +31098,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G30" s="16" t="inlineStr">
+      <c r="G29" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,143万
+$1143万
 $21,277/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $944万
@@ -31076,62 +31114,62 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I30" s="16" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,010万
+$1010万
 $20,658/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J30" s="16" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,667万
+$1667万
 $21,514/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,630万
+$1630万
 $20,319/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,733万
+$1733万
 $22,186/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,115万
+$1115万
 $21,912/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E31" s="16" t="inlineStr">
+      <c r="E30" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,628万
+$1628万
 $21,149/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F31" s="16" t="inlineStr">
+      <c r="F30" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $998万
@@ -31139,15 +31177,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G30" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,105万
+$1105万
 $20,585/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $968万
@@ -31155,62 +31193,62 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,035万
+$1035万
 $21,162/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J31" s="16" t="inlineStr">
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,709万
+$1709万
 $22,046/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,670万
+$1670万
 $20,820/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C32" s="16" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,676万
+$1676万
 $21,466/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,111万
+$1111万
 $21,819/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="E31" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,622万
+$1622万
 $21,058/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $965万
@@ -31218,15 +31256,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G32" s="16" t="inlineStr">
+      <c r="G31" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,132万
+$1132万
 $21,088/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $942万
@@ -31234,62 +31272,62 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I32" s="16" t="inlineStr">
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,030万
+$1030万
 $21,067/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J32" s="16" t="inlineStr">
+      <c r="J31" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,701万
+$1701万
 $21,954/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="65" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,616万
+$1616万
 $20,146/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C33" s="16" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,718万
+$1718万
 $21,996/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D33" s="16" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,106万
+$1106万
 $21,725/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E33" s="16" t="inlineStr">
+      <c r="E32" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,615万
+$1615万
 $20,969/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F33" s="16" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $989万
@@ -31297,15 +31335,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G32" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,123万
+$1123万
 $20,920/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="H32" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $931万
@@ -31313,62 +31351,62 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I32" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,026万
+$1026万
 $20,971/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J33" s="16" t="inlineStr">
+      <c r="J32" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,646万
+$1646万
 $21,245/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="65" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,609万
+$1609万
 $20,060/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,710万
+$1710万
 $21,900/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,101万
+$1101万
 $21,631/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="E33" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,608万
+$1608万
 $20,878/呎
 (25年-10月)</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $984万
@@ -31376,15 +31414,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G34" s="16" t="inlineStr">
+      <c r="G33" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,083万
+$1083万
 $20,168/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $953万
@@ -31392,7 +31430,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I34" s="16" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
 $992万
@@ -31400,54 +31438,54 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="J33" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,640万
+$1640万
 $21,156/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="65" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,641万
+$1641万
 $20,459/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C35" s="16" t="inlineStr">
+      <c r="C34" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,695万
+$1695万
 $21,706/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,060万
+$1060万
 $20,835/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E35" s="16" t="inlineStr">
+      <c r="E34" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,548万
+$1548万
 $20,108/呎
 (25年-05月)</t>
         </is>
       </c>
-      <c r="F35" s="16" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $948万
@@ -31455,15 +31493,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G34" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,074万
+$1074万
 $19,998/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H35" s="16" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $921万
@@ -31471,7 +31509,7 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
 $988万
@@ -31479,54 +31517,54 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,676万
+$1676万
 $21,619/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="65" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 802呎 (3房)
-$1,611万
+$1611万
 $20,087/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="inlineStr">
+      <c r="C35" s="20" t="inlineStr">
         <is>
           <t>B | 781呎 (3房)
-$1,676万
+$1676万
 $21,465/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>C | 509呎 (2房)
-$1,085万
+$1085万
 $21,322/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>D | 770呎 (3房)
-$1,564万
+$1564万
 $20,313/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>E | 474呎 (2房)
 $960万
@@ -31534,15 +31572,15 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="G36" s="16" t="inlineStr">
+      <c r="G35" s="20" t="inlineStr">
         <is>
           <t>F | 537呎 (2房)
-$1,138万
+$1138万
 $21,188/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="H36" s="16" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>G | 485呎 (2房)
 $940万
@@ -31550,18 +31588,18 @@
 (24年-11月)</t>
         </is>
       </c>
-      <c r="I36" s="16" t="inlineStr">
+      <c r="I35" s="20" t="inlineStr">
         <is>
           <t>H | 489呎 (2房)
-$1,082万
+$1082万
 $22,127/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="J36" s="16" t="inlineStr">
+      <c r="J35" s="20" t="inlineStr">
         <is>
           <t>J | 775呎 (3房)
-$1,604万
+$1604万
 $20,699/呎
 (24年-11月)</t>
         </is>
@@ -31569,7 +31607,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
